--- a/Data/raw/Western Australian Middens.xlsx
+++ b/Data/raw/Western Australian Middens.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\SNR_SDM\Data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D9FD8A5-D192-4402-90DB-C3A080C6B4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28FDE7-EEB1-41BC-BCB5-FD5CDF36A90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{999591E4-4701-4EF7-B33A-485E71C36D2F}"/>
   </bookViews>
@@ -195,24 +195,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -227,11 +215,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -549,849 +536,802 @@
   <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="70.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="27.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>113.43300000000001</v>
-      </c>
-      <c r="E2" s="3">
-        <v>-24.117000000000001</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>113.43</v>
+      </c>
+      <c r="E2" s="1">
+        <v>-24.12</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="B3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
         <v>113.8</v>
       </c>
-      <c r="E3" s="3">
-        <v>-23.117000000000001</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="1">
+        <v>-23.12</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>113.983</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="B4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>113.98</v>
+      </c>
+      <c r="E4" s="1">
         <v>-22.2</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3">
-        <v>113.983</v>
-      </c>
-      <c r="E5" s="3">
-        <v>-22.183</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="B5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>113.98</v>
+      </c>
+      <c r="E5" s="1">
+        <v>-22.18</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="B6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
         <v>114</v>
       </c>
-      <c r="E6" s="3">
-        <v>-22.216999999999999</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="1">
+        <v>-22.22</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
         <v>114</v>
       </c>
-      <c r="E7" s="3">
-        <v>-22.132999999999999</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="1">
+        <v>-22.13</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
-        <v>114.033</v>
-      </c>
-      <c r="E8" s="3">
-        <v>-22.016999999999999</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>114.03</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-22.02</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
         <v>113.3</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>-26.4</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3">
-        <v>113.583</v>
-      </c>
-      <c r="E10" s="3">
-        <v>-25.632999999999999</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>113.58</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-25.63</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>113.68300000000001</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>113.68</v>
+      </c>
+      <c r="E11" s="1">
         <v>-26.6</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>114.283</v>
-      </c>
-      <c r="E12" s="3">
-        <v>-25.983000000000001</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>114.28</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-25.98</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
         <v>115.15</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>-25.35</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3">
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1">
         <v>115.35</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>-24.75</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>115.583</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-29.082999999999998</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>115.58</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-29.08</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3">
-        <v>115.617</v>
-      </c>
-      <c r="E16" s="3">
-        <v>-28.117000000000001</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="1">
+        <v>115.62</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-28.12</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3">
-        <v>116.283</v>
-      </c>
-      <c r="E17" s="3">
-        <v>-27.466999999999999</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="1">
+        <v>116.28</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-27.47</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="3">
-        <v>116.767</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>116.77</v>
+      </c>
+      <c r="E18" s="1">
         <v>-29.2</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="1">
         <v>117.15</v>
       </c>
-      <c r="E19" s="3">
-        <v>-23.567</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="E19" s="1">
+        <v>-23.57</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="3">
-        <v>117.18300000000001</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-28.132999999999999</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>117.18</v>
+      </c>
+      <c r="E20" s="1">
+        <v>-28.13</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="1">
         <v>117.25</v>
       </c>
-      <c r="E21" s="3">
-        <v>-29.567</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E21" s="1">
+        <v>-29.57</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D22" s="3">
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
         <v>117.75</v>
       </c>
-      <c r="E22" s="3">
-        <v>-25.067</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="1">
+        <v>-25.07</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D23" s="3">
-        <v>117.917</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>117.92</v>
+      </c>
+      <c r="E23" s="1">
         <v>-24.05</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>55239</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="3">
-        <v>116.2833</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="C24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>116.28</v>
+      </c>
+      <c r="E24" s="1">
         <v>-27.6</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="H24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>55233</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D25" s="3">
+      <c r="C25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
         <v>117.9</v>
       </c>
-      <c r="E25" s="3">
-        <v>-29.916599999999999</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="1">
+        <v>-29.92</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H25" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>55197</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D26" s="3">
-        <v>122.9833</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-25.7166</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="C26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>122.98</v>
+      </c>
+      <c r="E26" s="1">
+        <v>-25.72</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H26" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>112.95</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>-25.75</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D28">
-        <v>113.43300000000001</v>
-      </c>
-      <c r="E28">
-        <v>-24.117000000000001</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="D28" s="1">
+        <v>113.43</v>
+      </c>
+      <c r="E28" s="1">
+        <v>-24.12</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>113.8</v>
       </c>
-      <c r="E29">
-        <v>-23.117000000000001</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="E29" s="1">
+        <v>-23.12</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>0</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>114.1</v>
       </c>
-      <c r="E30">
-        <v>-27.832999999999998</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="E30" s="1">
+        <v>-27.83</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
         <v>113.1</v>
       </c>
-      <c r="E31">
-        <v>-25.966999999999999</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" s="1">
+        <v>-25.97</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
         <v>113.3</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="1">
         <v>-26.4</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D33">
-        <v>113.583</v>
-      </c>
-      <c r="E33">
-        <v>-25.632999999999999</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="D33" s="1">
+        <v>113.58</v>
+      </c>
+      <c r="E33" s="1">
+        <v>-25.63</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D34">
-        <v>113.68300000000001</v>
-      </c>
-      <c r="E34">
+      <c r="D34" s="1">
+        <v>113.68</v>
+      </c>
+      <c r="E34" s="1">
         <v>-26.6</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B35" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D35">
-        <v>114.283</v>
-      </c>
-      <c r="E35">
-        <v>-25.983000000000001</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="D35" s="1">
+        <v>114.28</v>
+      </c>
+      <c r="E35" s="1">
+        <v>-25.98</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B36" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D36">
-        <v>115.617</v>
-      </c>
-      <c r="E36">
-        <v>-28.117000000000001</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="D36" s="1">
+        <v>115.62</v>
+      </c>
+      <c r="E36" s="1">
+        <v>-28.12</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B37" t="s">
-        <v>0</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D37">
-        <v>117.18300000000001</v>
-      </c>
-      <c r="E37">
-        <v>-28.132999999999999</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="D37" s="1">
+        <v>117.18</v>
+      </c>
+      <c r="E37" s="1">
+        <v>-28.13</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="A38" s="1">
         <v>12567</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D38">
-        <v>140.783331</v>
-      </c>
-      <c r="E38">
-        <v>-37.833334000000001</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="D38" s="1">
+        <v>140.78</v>
+      </c>
+      <c r="E38" s="1">
+        <v>-37.83</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="1" t="s">
         <v>46</v>
       </c>
     </row>
